--- a/example/input.xlsx
+++ b/example/input.xlsx
@@ -454,7 +454,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
-    <col width="13" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -884,16 +884,16 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
-    <col width="13" customWidth="1" min="2" max="2"/>
-    <col width="13" customWidth="1" min="3" max="3"/>
-    <col width="13" customWidth="1" min="4" max="4"/>
-    <col width="13" customWidth="1" min="5" max="5"/>
-    <col width="13" customWidth="1" min="6" max="6"/>
-    <col width="13" customWidth="1" min="7" max="7"/>
-    <col width="13" customWidth="1" min="8" max="8"/>
-    <col width="13" customWidth="1" min="9" max="9"/>
-    <col width="13" customWidth="1" min="10" max="10"/>
-    <col width="13" customWidth="1" min="11" max="11"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="18" customWidth="1" min="5" max="5"/>
+    <col width="18" customWidth="1" min="6" max="6"/>
+    <col width="18" customWidth="1" min="7" max="7"/>
+    <col width="18" customWidth="1" min="8" max="8"/>
+    <col width="18" customWidth="1" min="9" max="9"/>
+    <col width="18" customWidth="1" min="10" max="10"/>
+    <col width="18" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1099,7 +1099,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
-    <col width="13" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1120,10 +1120,8 @@
           <t>Max sessions per peer</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="B2" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="3">
@@ -1132,10 +1130,8 @@
           <t>Max sessions per group per week</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="B3" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="4">
@@ -1161,7 +1157,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A25"/>
+  <dimension ref="A1:A26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="90" customWidth="1" min="1" max="1"/>
@@ -1178,7 +1174,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Groups: one row per class split, plus the class it belongs to.</t>
+          <t>Groups: one row per class split, plus the class it belongs to. Already filled in.</t>
         </is>
       </c>
     </row>
@@ -1220,107 +1216,114 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Calendar: rows are classes, columns are weeks; an x marks a class trip. Please list</t>
+          <t>Calendar: rows are classes, columns are weeks; an x marks a class trip. Both the</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>both the tutored classes and the classes the peers come from.</t>
+          <t>tutored classes and the peer classes are listed - please keep them, the planner</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Settings: optional. 'Max sessions per peer' is the default limit for peers that</t>
+          <t>reads both.</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>leave their own limit blank; 'Max sessions per group per week' caps how many</t>
+          <t>Settings: 'Max sessions per peer' is the default limit for peers that leave their</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>sessions one class group may have in the same week (blank = no cap); 'Blackout</t>
+          <t>own limit blank; 'Max sessions per group per week' caps how many sessions one class</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>weeks' are weeks with no mentoring at all (holidays, exam weeks, project weeks).</t>
-        </is>
-      </c>
-    </row>
-    <row r="15"/>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>The rules:</t>
-        </is>
-      </c>
-    </row>
+          <t>group may have in the same week (blank = no cap); 'Blackout weeks' are weeks with no</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>mentoring at all (holidays, exam weeks, project weeks).</t>
+        </is>
+      </c>
+    </row>
+    <row r="16"/>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t xml:space="preserve">  A room exists only in weeks where a TUTORED class is on a trip - a trip of a</t>
+          <t>The rules:</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t xml:space="preserve">  peer's class does not open a room, it only makes that peer unavailable.</t>
+          <t xml:space="preserve">  A room exists only in weeks where a TUTORED class is on a trip - a trip of a</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t xml:space="preserve">  A group never meets in a week when its own class is away; a peer group never meets</t>
+          <t xml:space="preserve">  peer's class does not open a room, it only makes that peer unavailable.</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t xml:space="preserve">  in a week when any of its pupils' classes is away.</t>
+          <t xml:space="preserve">  A group never meets in a week when its own class is away; a peer group never meets</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Every group does every topic exactly once, so it has one session per topic. A</t>
+          <t xml:space="preserve">  in a week when any of its pupils' classes is away.</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
+          <t xml:space="preserve">  Every group does every topic exactly once, so it has one session per topic. A</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
           <t xml:space="preserve">  week may hold several sessions for one group; the planner spreads them where it can.</t>
         </is>
       </c>
     </row>
-    <row r="23"/>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>Run: uv run python main.py example/input.xlsx</t>
-        </is>
-      </c>
-    </row>
+    <row r="24"/>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>The sheets Plan, Sessions, Loads, Overview and Notes are written for you.</t>
+          <t>Fill in the peer surnames and the trips, then run the planner. The sheets Plan,</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Sessions, Loads, Overview and Notes are written for you.</t>
         </is>
       </c>
     </row>

--- a/example/input.xlsx
+++ b/example/input.xlsx
@@ -1157,7 +1157,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A26"/>
+  <dimension ref="A1:A29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="90" customWidth="1" min="1" max="1"/>
@@ -1230,100 +1230,121 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>reads both.</t>
+          <t>reads both. The template starts with one example trip per tutored class, each in a</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Settings: 'Max sessions per peer' is the default limit for peers that leave their</t>
+          <t>different week, so it can be planned right away - replace them with the real ones.</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>own limit blank; 'Max sessions per group per week' caps how many sessions one class</t>
+          <t>Settings: 'Max sessions per peer' is the default limit for peers that leave their</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>group may have in the same week (blank = no cap); 'Blackout weeks' are weeks with no</t>
+          <t>own limit blank; 'Max sessions per group per week' caps how many sessions one class</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
+          <t>group may have in the same week (blank = no cap); 'Blackout weeks' are weeks with no</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
           <t>mentoring at all (holidays, exam weeks, project weeks).</t>
         </is>
       </c>
     </row>
-    <row r="16"/>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>The rules:</t>
-        </is>
-      </c>
-    </row>
+    <row r="17"/>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t xml:space="preserve">  A room exists only in weeks where a TUTORED class is on a trip - a trip of a</t>
+          <t>The rules:</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t xml:space="preserve">  peer's class does not open a room, it only makes that peer unavailable.</t>
+          <t xml:space="preserve">  A room exists only in weeks where a TUTORED class is on a trip - a trip of a</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t xml:space="preserve">  A group never meets in a week when its own class is away; a peer group never meets</t>
+          <t xml:space="preserve">  peer's class does not open a room, it only makes that peer unavailable.</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t xml:space="preserve">  in a week when any of its pupils' classes is away.</t>
+          <t xml:space="preserve">  A group never meets in a week when its own class is away; a peer group never meets</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Every group does every topic exactly once, so it has one session per topic. A</t>
+          <t xml:space="preserve">  in a week when any of its pupils' classes is away.</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
+          <t xml:space="preserve">  Every group does every topic exactly once, so it has one session per topic. A</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
           <t xml:space="preserve">  week may hold several sessions for one group; the planner spreads them where it can.</t>
         </is>
       </c>
     </row>
-    <row r="24"/>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>Fill in the peer surnames and the trips, then run the planner. The sheets Plan,</t>
-        </is>
-      </c>
-    </row>
+    <row r="25"/>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Sessions, Loads, Overview and Notes are written for you.</t>
+          <t>Fill in the peer surnames and the trips, then run the planner: double click</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>mentoring-planner.exe and a window opens where you pick this file, or run</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>'python main.py &lt;this file&gt;' in a shell. The sheets Plan, Sessions, Loads, Overview</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>and Notes are written for you - they are replaced on every run.</t>
         </is>
       </c>
     </row>
